--- a/public/files/warehouse-audit-working-pack.xlsx
+++ b/public/files/warehouse-audit-working-pack.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R31b0e689c8fe41bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope and criteria" sheetId="2" r:id="R74207fbe94e24b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist and evidence" sheetId="3" r:id="Rf2c577f1d9374a9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings and actions" sheetId="4" r:id="Rc449a8c5802741db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Management review" sheetId="5" r:id="R05e228dcce544114"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked examples" sheetId="6" r:id="R99820d8006094f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R008e8739509946fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope and criteria" sheetId="2" r:id="Rf878174ba3d5483a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist and evidence" sheetId="3" r:id="Rac38dfd486924671"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings and actions" sheetId="4" r:id="Rf7e4a5b2f9eb42f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Management review" sheetId="5" r:id="R1ea0b476166e4b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked examples" sheetId="6" r:id="Re7f550447ad34585"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1027,7 +1027,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="R48c239dc96144bb1"/>
+    <tablePart r:id="Rf5a8a04dfafb4067"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1628,9 +1628,9 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="3">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cc7513b8fc7430b"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6fbfdd33eba4f6c"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a4e19949f374157"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10aaa44b26664f7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R231fc6554b6d4f79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33a78978e3db459a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3470,8 +3470,8 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart r:id="Rd20b3f6a005d41d6"/>
-    <tablePart r:id="R8d18320d3b7f4610"/>
+    <tablePart r:id="Rf098649c98d74f22"/>
+    <tablePart r:id="R7a8228667720427c"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4836,9 +4836,9 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="3">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ae7a6b90c35430a"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1760d98085fc4cef"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fae9c090dd44601"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R495a68d7b72e45f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66ac0f93a5974ad8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f25e9d2faa34f9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5130,8 +5130,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red59d1b753ff4e59"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e0902d83287447b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f7afc5d06c34a87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76cae2a65fd64d5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5181,7 +5181,7 @@
         <x:v>Example status</x:v>
       </x:c>
       <x:c r="B7" s="29" t="str">
-        <x:v>Fictional worked example — investigation remains open</x:v>
+        <x:v>Fictional worked example — correction and limited verification recorded</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
@@ -5189,7 +5189,7 @@
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>Show how a confirmed difference can be recorded without inventing its cause or treating a balance adjustment as closure.</x:v>
+        <x:v>Follow one evidenced stock difference through correction, a process action and verification. Keep older recurrences unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -5209,7 +5209,7 @@
         <x:v>Site or area alias</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>Example bin A-01</x:v>
+        <x:v>Example bin A01</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="45" customHeight="1">
@@ -5217,7 +5217,7 @@
         <x:v>Review date or period</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>Comparison time and review dates not yet recorded.</x:v>
+        <x:v>Count comparison: 6 October 2026, 09:00. Follow-up: 9 October 2026, 15:00.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="45" customHeight="1">
@@ -5225,7 +5225,7 @@
         <x:v>Operating conditions</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>Movement timing and unit history remain to be reconciled.</x:v>
+        <x:v>One unit dispatched on 5 October at 16:40. Its stock issue was still pending at the count.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="45" customHeight="1">
@@ -5233,7 +5233,7 @@
         <x:v>Coverage and sample</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>SKU-104 in bin A-01; count, recount and selected receipt/issue records. Linked checks INV01, INV02 and INV03.</x:v>
+        <x:v>SKU104, bin A01. Count/recount and transaction trail; follow-up covers 20 dispatches on 7–9 October across three shifts. Checks INV01–03.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="45" customHeight="1">
@@ -5241,7 +5241,7 @@
         <x:v>Exclusions and limits</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>This one-item example does not establish the condition of the whole inventory.</x:v>
+        <x:v>Older discrepancies remain unexplained. This item and limited follow-up sample do not establish performance across all stock or shifts.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="45" customHeight="1">
@@ -5249,7 +5249,7 @@
         <x:v>Criteria and versions</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>Site inventory procedure identified; version, comparison boundary and applicable steps not yet recorded.</x:v>
+        <x:v>Fictional procedure INV04 v3: post each stock issue before dispatch. Compare the same item, unit, location and time.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="45" customHeight="1">
@@ -5257,7 +5257,7 @@
         <x:v>Reviewer and evidence providers</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>Reviewer and any required independent verification not yet assigned.</x:v>
+        <x:v>Inventory lead traces C104, RC104, S104, P418, D418 and Q418. Warehouse manager verifies the follow-up in V104.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="45" customHeight="1">
@@ -5265,7 +5265,7 @@
         <x:v>Action responsibilities</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>Inventory lead, working with the process/system owner.</x:v>
+        <x:v>Inventory lead owns the handover change and pending-issue review, due 6 October 2026, 17:00.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="45" customHeight="1">
@@ -5273,7 +5273,7 @@
         <x:v>Decision owner</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>Adjustment or resource authority to be established under the site's procedure.</x:v>
+        <x:v>Inventory manager authorises posting the one missing issue on 6 October 2026, 11:00.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
@@ -5323,7 +5323,7 @@
         <x:v>Criterion / reference</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>Site inventory procedure. Version and effective comparison criteria not yet recorded.</x:v>
+        <x:v>Fictional site procedure INV04 v3 requires each stock issue to be posted before dispatch.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="60" customHeight="1">
@@ -5331,7 +5331,7 @@
         <x:v>Observation</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>The physical count for SKU-104 in bin A-01 is 11 units; the inventory record shows 12. A recount confirms 11.</x:v>
+        <x:v>At 09:00 on 6 October 2026, C104 and independent recount RC104 show 11 each of SKU104 in bin A01. Snapshot S104 shows 12.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
@@ -5339,7 +5339,7 @@
         <x:v>Evidence obtained</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
-        <x:v>Count note, recount, stock-record comparison and references to selected receipt/issue records in this fictional case.</x:v>
+        <x:v>P418 and D418 record one unit leaving on 5 October at 16:40. Q418 shows that issue still pending at the count.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="60" customHeight="1">
@@ -5347,7 +5347,7 @@
         <x:v>Evidence still needed</x:v>
       </x:c>
       <x:c r="B29" s="7" t="str">
-        <x:v>Reconcile receipt/issue timing, the record snapshot and unit/pack definitions at the comparison point.</x:v>
+        <x:v>Investigate the separate older recurrences. This transaction trail does not explain those earlier differences.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="60" customHeight="1">
@@ -5355,7 +5355,7 @@
         <x:v>Uncertainty</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
-        <x:v>The difference is confirmed. Its cause, full transaction boundary and required action remain unresolved.</x:v>
+        <x:v>The unposted issue explains this one-unit difference. Why it remained pending and the causes of older recurrences are not established.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
@@ -5363,7 +5363,7 @@
         <x:v>Possible cause (hypothesis)</x:v>
       </x:c>
       <x:c r="B31" s="7" t="str">
-        <x:v>Hypothesis only: unit-of-measure or transaction-timing issue. Neither is established.</x:v>
+        <x:v>Evidence confirms one unposted issue. It does not establish fraud or a root cause for all recurring discrepancies.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="60" customHeight="1">
@@ -5371,7 +5371,7 @@
         <x:v>Next action</x:v>
       </x:c>
       <x:c r="B32" s="7" t="str">
-        <x:v>Compare the receipt/issue trail and unit definitions with the process/system owner. Retain the explanation supported by evidence. Handle any balance adjustment separately under the authorised process.</x:v>
+        <x:v>Post the single missing issue with approval. Give handover a named owner and review pending issues before release. Retain older cases for investigation.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
@@ -5379,7 +5379,7 @@
         <x:v>Action type</x:v>
       </x:c>
       <x:c r="B33" s="7" t="str">
-        <x:v>Investigation</x:v>
+        <x:v>Authorised correction, corrective action and verification</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
@@ -5395,7 +5395,7 @@
         <x:v>Target date</x:v>
       </x:c>
       <x:c r="B35" s="7" t="str">
-        <x:v>Not yet agreed</x:v>
+        <x:v>6 October 2026, 17:00, for handover ownership and the pending-issue review.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
@@ -5403,7 +5403,7 @@
         <x:v>Urgency</x:v>
       </x:c>
       <x:c r="B36" s="7" t="str">
-        <x:v>Not assessed</x:v>
+        <x:v>Inventory manager requires the record correction and control change on 6 October. No wider urgency conclusion is made.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="42" customHeight="1">
@@ -5411,7 +5411,7 @@
         <x:v>Work state</x:v>
       </x:c>
       <x:c r="B37" s="7" t="str">
-        <x:v>Open — investigation not completed</x:v>
+        <x:v>6 October: manager approves posting at 11:00. Records then show 11. H104 records named handover ownership and pre-release pending-issue review in use by 17:00.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="60" customHeight="1">
@@ -5419,7 +5419,7 @@
         <x:v>Verification method</x:v>
       </x:c>
       <x:c r="B38" s="7" t="str">
-        <x:v>After an evidenced action is chosen, examine subsequent relevant transactions and counts against the agreed criterion. Define the sample and timing before verification.</x:v>
+        <x:v>V104: compare 20 dispatches on 7–9 October across three shifts with INV04 v3. Check issue posting before release and recount the selected bin.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
@@ -5427,7 +5427,7 @@
         <x:v>Verification owner</x:v>
       </x:c>
       <x:c r="B39" s="7" t="str">
-        <x:v>Not yet assigned</x:v>
+        <x:v>Warehouse manager</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="42" customHeight="1">
@@ -5435,7 +5435,7 @@
         <x:v>Verification date</x:v>
       </x:c>
       <x:c r="B40" s="7" t="str">
-        <x:v>Not yet agreed</x:v>
+        <x:v>9 October 2026, 15:00</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
@@ -5443,7 +5443,7 @@
         <x:v>Verification result</x:v>
       </x:c>
       <x:c r="B41" s="7" t="str">
-        <x:v>Pending — no effectiveness conclusion</x:v>
+        <x:v>Effective in the examined sample: all 20 issues posted before release and the selected bin matches. Older recurrences remain unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
@@ -5451,7 +5451,7 @@
         <x:v>Decision / resources needed</x:v>
       </x:c>
       <x:c r="B42" s="7" t="str">
-        <x:v>Establish adjustment authority and any process/system decision once the evidence is reviewed.</x:v>
+        <x:v>The manager approves posting the one missing issue. No additional balance adjustment is made, which would double-count the correction.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
@@ -5459,7 +5459,7 @@
         <x:v>Decision owner</x:v>
       </x:c>
       <x:c r="B43" s="7" t="str">
-        <x:v>Not yet established</x:v>
+        <x:v>Inventory manager for correction authority; inventory lead for the process action and older-case investigation.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="30" customHeight="1">
@@ -5471,7 +5471,7 @@
         <x:v>Management note</x:v>
       </x:c>
       <x:c r="B45" s="7" t="str">
-        <x:v>Keep the one-unit difference, uncertain explanation and missing verification assignment visible. The case does not establish a missed pick, loss or successful fix.</x:v>
+        <x:v>Close this recorded correction and sampled follow-up. Keep older recurrences open. V104 supports the result only for the examined sample.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="30" customHeight="1">
@@ -5501,7 +5501,7 @@
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B50" s="7" t="str">
-        <x:v>Bring service, storage and billing evidence to one decision while retaining separate criteria, owners and unanswered questions.</x:v>
+        <x:v>Bring service, storage and billing evidence to a renewal review. Show a verified credit alongside service and storage questions that remain open.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="30" customHeight="1">
@@ -5529,7 +5529,7 @@
         <x:v>Review date or period</x:v>
       </x:c>
       <x:c r="B54" s="7" t="str">
-        <x:v>Renewal review period, shipment sample and billed period not yet agreed.</x:v>
+        <x:v>Review as at 8 October 2026. Service and billed-activity period: 1–7 October 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="45" customHeight="1">
@@ -5537,7 +5537,7 @@
         <x:v>Operating conditions</x:v>
       </x:c>
       <x:c r="B55" s="7" t="str">
-        <x:v>Workload, staffing and exception context to be obtained for selected shipments.</x:v>
+        <x:v>Investigate the four late orders. Product acceptability remains unresolved because the 2 October condition record is missing.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="45" customHeight="1">
@@ -5545,7 +5545,7 @@
         <x:v>Coverage and sample</x:v>
       </x:c>
       <x:c r="B56" s="7" t="str">
-        <x:v>Selected late dispatches, goods affected by the storage concern and disputed invoice lines. Linked checks FLOW03, FLOW04, GOODS02, GOODS04, CONTROL03 and CONTROL04.</x:v>
+        <x:v>12 orders, goods affected by the 2 October record gap and one invoice line for 120 pallet-days. Checks FLOW03–04, GOODS02, GOODS04 and CONTROL03–04.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="45" customHeight="1">
@@ -5553,7 +5553,7 @@
         <x:v>Exclusions and limits</x:v>
       </x:c>
       <x:c r="B57" s="7" t="str">
-        <x:v>This review has not established all provider qualifications or every product, legal or commercial requirement.</x:v>
+        <x:v>No conclusion on all provider qualifications or all shipments. Fictional invoice amounts exclude VAT and other lines.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="45" customHeight="1">
@@ -5561,7 +5561,7 @@
         <x:v>Criteria and versions</x:v>
       </x:c>
       <x:c r="B58" s="7" t="str">
-        <x:v>Dispatch commitment, goods/customer storage requirement and applicable contract/rate version remain to be obtained and assigned to the relevant issue.</x:v>
+        <x:v>SLA12 v2: orders ready for 17:00 dispatch. CS2 v2: customer dry-storage requirement. Signed rate v2: £1.50 per pallet-day from 1 October.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="45" customHeight="1">
@@ -5569,7 +5569,7 @@
         <x:v>Reviewer and evidence providers</x:v>
       </x:c>
       <x:c r="B59" s="7" t="str">
-        <x:v>Service, product/quality and commercial/finance owners provide evidence. Review responsibilities and any specialist assessment to be agreed.</x:v>
+        <x:v>Service lead checks order/staging/handover records. Quality lead assesses the record gap. Commercial lead reconciles billing; finance controller checks CN82.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="45" customHeight="1">
@@ -5577,7 +5577,7 @@
         <x:v>Action responsibilities</x:v>
       </x:c>
       <x:c r="B60" s="7" t="str">
-        <x:v>A separate responsible owner for each issue.</x:v>
+        <x:v>Service lead: report by 10 October. Quality lead: assessment by 9 October. Commercial lead: credit and contract timetable/options.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="45" customHeight="1">
@@ -5585,7 +5585,7 @@
         <x:v>Decision owner</x:v>
       </x:c>
       <x:c r="B61" s="7" t="str">
-        <x:v>Logistics director for renewal; other approval authorities to be established where required.</x:v>
+        <x:v>Logistics director requests the service plan and quality assessment on 8 October before a final renewal decision.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="30" customHeight="1">
@@ -5627,7 +5627,7 @@
         <x:v>Review status</x:v>
       </x:c>
       <x:c r="B67" s="7" t="str">
-        <x:v>Inconclusive or conflicting evidence</x:v>
+        <x:v>Concern found</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="42" customHeight="1">
@@ -5635,7 +5635,7 @@
         <x:v>Criterion / reference</x:v>
       </x:c>
       <x:c r="B68" s="7" t="str">
-        <x:v>Agreed dispatch commitment and relevant agreement version not yet attached.</x:v>
+        <x:v>Fictional SLA12 v2 requires the selected orders to be ready for 17:00 dispatch.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="60" customHeight="1">
@@ -5643,7 +5643,7 @@
         <x:v>Observation</x:v>
       </x:c>
       <x:c r="B69" s="7" t="str">
-        <x:v>Recent dispatches are reported late. The selected shipment records have not yet been compared with the agreed commitment.</x:v>
+        <x:v>Four of 12 selected orders from 1–7 October 2026 were late against the agreed dispatch-readiness commitment.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="42" customHeight="1">
@@ -5651,7 +5651,7 @@
         <x:v>Evidence obtained</x:v>
       </x:c>
       <x:c r="B70" s="7" t="str">
-        <x:v>Reported service concern in this fictional case; supporting timestamps not yet attached.</x:v>
+        <x:v>Order, staging and handover records for the 12 orders establish the four exceptions against SLA12 v2.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="60" customHeight="1">
@@ -5659,7 +5659,7 @@
         <x:v>Evidence still needed</x:v>
       </x:c>
       <x:c r="B71" s="7" t="str">
-        <x:v>Agreed commitment, order-release and actual dispatch timestamps, workload, staffing and exception records for the selected shipments.</x:v>
+        <x:v>Service lead to examine staffing, workload, queues and exceptions around the four late orders and propose a supported service plan.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="60" customHeight="1">
@@ -5667,7 +5667,7 @@
         <x:v>Uncertainty</x:v>
       </x:c>
       <x:c r="B72" s="7" t="str">
-        <x:v>Extent, contractual significance and reason for the delays remain unconfirmed.</x:v>
+        <x:v>The four exceptions are established within this sample. Their cause and wider service performance remain under investigation.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="42" customHeight="1">
@@ -5675,7 +5675,7 @@
         <x:v>Possible cause (hypothesis)</x:v>
       </x:c>
       <x:c r="B73" s="7" t="str">
-        <x:v>Not established</x:v>
+        <x:v>Not yet established. The observed lateness does not identify a particular operating cause.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="60" customHeight="1">
@@ -5683,7 +5683,7 @@
         <x:v>Next action</x:v>
       </x:c>
       <x:c r="B74" s="7" t="str">
-        <x:v>Obtain and compare the selected shipment records with the commitment; identify the constraint supported by the evidence.</x:v>
+        <x:v>Service lead reports the evidence, remaining cause questions and proposed plan to the director by 10 October 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
@@ -5699,7 +5699,7 @@
         <x:v>Responsible owner</x:v>
       </x:c>
       <x:c r="B76" s="7" t="str">
-        <x:v>Service owner</x:v>
+        <x:v>Service lead</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="42" customHeight="1">
@@ -5707,7 +5707,7 @@
         <x:v>Target date</x:v>
       </x:c>
       <x:c r="B77" s="7" t="str">
-        <x:v>Not yet agreed</x:v>
+        <x:v>10 October 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
@@ -5715,7 +5715,7 @@
         <x:v>Urgency</x:v>
       </x:c>
       <x:c r="B78" s="7" t="str">
-        <x:v>Not assessed</x:v>
+        <x:v>Director requires the service plan before the final renewal decision.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
@@ -5723,7 +5723,7 @@
         <x:v>Work state</x:v>
       </x:c>
       <x:c r="B79" s="7" t="str">
-        <x:v>Open — evidence requested</x:v>
+        <x:v>Open as at 8 October: investigation and service plan due 10 October.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="60" customHeight="1">
@@ -5731,7 +5731,7 @@
         <x:v>Verification method</x:v>
       </x:c>
       <x:c r="B80" s="7" t="str">
-        <x:v>Once an action and service criterion are agreed, compare later relevant shipment performance and exception records. Verification period not yet established.</x:v>
+        <x:v>After agreeing the plan, warehouse manager checks later order/staging/handover records against SLA12 v2. Agree coverage and timing with the plan.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="42" customHeight="1">
@@ -5739,7 +5739,7 @@
         <x:v>Verification owner</x:v>
       </x:c>
       <x:c r="B81" s="7" t="str">
-        <x:v>Not yet assigned</x:v>
+        <x:v>Warehouse manager</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="42" customHeight="1">
@@ -5747,7 +5747,7 @@
         <x:v>Verification date</x:v>
       </x:c>
       <x:c r="B82" s="7" t="str">
-        <x:v>Not yet agreed</x:v>
+        <x:v>To be agreed after the service plan</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="42" customHeight="1">
@@ -5763,7 +5763,7 @@
         <x:v>Decision / resources needed</x:v>
       </x:c>
       <x:c r="B84" s="7" t="str">
-        <x:v>Consider any evidenced resource or service condition as part of renewal.</x:v>
+        <x:v>Director requests a service plan before final renewal. Commercial lead checks the contract timetable and available options.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="42" customHeight="1">
@@ -5821,7 +5821,7 @@
         <x:v>Criterion / reference</x:v>
       </x:c>
       <x:c r="B92" s="7" t="str">
-        <x:v>Actual product/customer storage requirement and its applicable version not yet established.</x:v>
+        <x:v>Fictional customer requirement CS2 v2 specifies dry storage for the affected goods.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="60" customHeight="1">
@@ -5829,7 +5829,7 @@
         <x:v>Observation</x:v>
       </x:c>
       <x:c r="B93" s="7" t="str">
-        <x:v>A customer has raised a storage concern. The affected goods, location and acceptability have not yet been established.</x:v>
+        <x:v>The 2 October 2026 condition record is missing for the affected goods. The available evidence cannot establish acceptability.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="42" customHeight="1">
@@ -5837,7 +5837,7 @@
         <x:v>Evidence obtained</x:v>
       </x:c>
       <x:c r="B94" s="7" t="str">
-        <x:v>Reported customer concern in this fictional case; supporting condition records not yet attached.</x:v>
+        <x:v>CS2 v2 and the condition-record review identify the specific 2 October gap.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="60" customHeight="1">
@@ -5845,7 +5845,7 @@
         <x:v>Evidence still needed</x:v>
       </x:c>
       <x:c r="B95" s="7" t="str">
-        <x:v>Affected goods/location, applicable storage requirement, monitoring records, reported exception and competent assessment of acceptability.</x:v>
+        <x:v>Quality lead to assess the affected goods, remaining condition evidence and any action needed under CS2 v2.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="60" customHeight="1">
@@ -5853,7 +5853,7 @@
         <x:v>Uncertainty</x:v>
       </x:c>
       <x:c r="B96" s="7" t="str">
-        <x:v>The concern does not establish product condition, a breached requirement or the required disposition.</x:v>
+        <x:v>Missing evidence does not establish acceptable or unacceptable goods. Product acceptability and any disposition remain for quality assessment.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
@@ -5869,7 +5869,7 @@
         <x:v>Next action</x:v>
       </x:c>
       <x:c r="B98" s="7" t="str">
-        <x:v>Establish the applicable requirement, assess the affected goods and determine any action and verification needed.</x:v>
+        <x:v>Quality lead assesses the affected goods and evidence gap under CS2 v2 and reports to the director by 9 October 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="42" customHeight="1">
@@ -5885,7 +5885,7 @@
         <x:v>Responsible owner</x:v>
       </x:c>
       <x:c r="B100" s="7" t="str">
-        <x:v>Product/quality owner</x:v>
+        <x:v>Quality lead</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="42" customHeight="1">
@@ -5893,7 +5893,7 @@
         <x:v>Target date</x:v>
       </x:c>
       <x:c r="B101" s="7" t="str">
-        <x:v>Not yet agreed</x:v>
+        <x:v>9 October 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="42" customHeight="1">
@@ -5901,7 +5901,7 @@
         <x:v>Urgency</x:v>
       </x:c>
       <x:c r="B102" s="7" t="str">
-        <x:v>Not assessed</x:v>
+        <x:v>Director requires the quality assessment before final renewal. Quality lead determines any response needed for the goods.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="42" customHeight="1">
@@ -5909,7 +5909,7 @@
         <x:v>Work state</x:v>
       </x:c>
       <x:c r="B103" s="7" t="str">
-        <x:v>Open — requirement and assessment outstanding</x:v>
+        <x:v>Open as at 8 October: quality assessment due 9 October.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="60" customHeight="1">
@@ -5917,7 +5917,7 @@
         <x:v>Verification method</x:v>
       </x:c>
       <x:c r="B104" s="7" t="str">
-        <x:v>Define the evidence needed to verify the chosen action against the actual storage requirement; method remains to be agreed by the responsible assessor.</x:v>
+        <x:v>Quality lead defines any required action and evidence of its effectiveness against CS2 v2 after assessing the affected goods.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="42" customHeight="1">
@@ -5925,7 +5925,7 @@
         <x:v>Verification owner</x:v>
       </x:c>
       <x:c r="B105" s="7" t="str">
-        <x:v>Not yet assigned</x:v>
+        <x:v>Quality lead; any additional assessor to be identified through the assessment.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="42" customHeight="1">
@@ -5933,7 +5933,7 @@
         <x:v>Verification date</x:v>
       </x:c>
       <x:c r="B106" s="7" t="str">
-        <x:v>Not yet agreed</x:v>
+        <x:v>To be agreed after the quality assessment</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="42" customHeight="1">
@@ -5949,7 +5949,7 @@
         <x:v>Decision / resources needed</x:v>
       </x:c>
       <x:c r="B108" s="7" t="str">
-        <x:v>Bring the assessment, required action and remaining uncertainty into the renewal review.</x:v>
+        <x:v>Director requests the quality assessment before final renewal. Keep the condition-record gap and any product decision visible.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="42" customHeight="1">
@@ -5957,7 +5957,7 @@
         <x:v>Decision owner</x:v>
       </x:c>
       <x:c r="B109" s="7" t="str">
-        <x:v>Logistics director; product disposition authority not yet established</x:v>
+        <x:v>Logistics director for renewal; quality lead to establish the required product decision and authority.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="30" customHeight="1">
@@ -5999,7 +5999,7 @@
         <x:v>Review status</x:v>
       </x:c>
       <x:c r="B115" s="7" t="str">
-        <x:v>Inconclusive or conflicting evidence</x:v>
+        <x:v>Concern found</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="42" customHeight="1">
@@ -6007,7 +6007,7 @@
         <x:v>Criterion / reference</x:v>
       </x:c>
       <x:c r="B116" s="7" t="str">
-        <x:v>Applicable contract/rate version, charging basis and billed period not yet attached.</x:v>
+        <x:v>Signed fictional rate v2, effective 1 October 2026: £1.50 per pallet-day for the same unit and billed period.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="60" customHeight="1">
@@ -6015,7 +6015,7 @@
         <x:v>Observation</x:v>
       </x:c>
       <x:c r="B117" s="7" t="str">
-        <x:v>Some invoice charges are disputed. The relevant invoice lines have not yet been reconciled to the agreement and activity records.</x:v>
+        <x:v>Invoice bills 120 pallet-days at £2 = £240. Activity records confirm 120. Rate v2 gives 120 × £1.50 = £180, a £60 difference.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="42" customHeight="1">
@@ -6023,7 +6023,7 @@
         <x:v>Evidence obtained</x:v>
       </x:c>
       <x:c r="B118" s="7" t="str">
-        <x:v>Reported billing dispute in this fictional case; selected invoice and activity references not yet attached.</x:v>
+        <x:v>Invoice line, matching 1–7 October activity records, signed rate v2 and obsolete v1 identify the rate error. CN82 records the agreed £60 credit.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="60" customHeight="1">
@@ -6031,7 +6031,7 @@
         <x:v>Evidence still needed</x:v>
       </x:c>
       <x:c r="B119" s="7" t="str">
-        <x:v>Contract/rate version, invoice lines, charging units, movement/storage/service records for the billed period and documented exceptions.</x:v>
+        <x:v>None for this reconciled line and credit. Other invoice lines and VAT are outside the example.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="60" customHeight="1">
@@ -6039,7 +6039,7 @@
         <x:v>Uncertainty</x:v>
       </x:c>
       <x:c r="B120" s="7" t="str">
-        <x:v>Interpretation, entitlement and any adjustment remain unresolved. No saving has been established.</x:v>
+        <x:v>The fictional calculation excludes VAT and other lines. It establishes no external contract entitlement or wider ROI.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="42" customHeight="1">
@@ -6047,7 +6047,7 @@
         <x:v>Possible cause (hypothesis)</x:v>
       </x:c>
       <x:c r="B121" s="7" t="str">
-        <x:v>Not established</x:v>
+        <x:v>Obsolete v1 rate was used instead of signed v2. The source of that rate-selection error is not established.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="60" customHeight="1">
@@ -6055,7 +6055,7 @@
         <x:v>Next action</x:v>
       </x:c>
       <x:c r="B122" s="7" t="str">
-        <x:v>Reconcile the selected invoice lines and charging units with the agreement and activity evidence; record any interpretation needing a decision.</x:v>
+        <x:v>Commercial lead agrees CN82 for £60 on 8 October. Finance controller checks the credit and net £180 on the same day.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="42" customHeight="1">
@@ -6063,7 +6063,7 @@
         <x:v>Action type</x:v>
       </x:c>
       <x:c r="B123" s="7" t="str">
-        <x:v>Investigation</x:v>
+        <x:v>Agreed billing correction and verification</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="42" customHeight="1">
@@ -6071,7 +6071,7 @@
         <x:v>Responsible owner</x:v>
       </x:c>
       <x:c r="B124" s="7" t="str">
-        <x:v>Commercial/finance owner</x:v>
+        <x:v>Commercial lead</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="42" customHeight="1">
@@ -6079,7 +6079,7 @@
         <x:v>Target date</x:v>
       </x:c>
       <x:c r="B125" s="7" t="str">
-        <x:v>Not yet agreed</x:v>
+        <x:v>8 October 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="42" customHeight="1">
@@ -6087,7 +6087,7 @@
         <x:v>Urgency</x:v>
       </x:c>
       <x:c r="B126" s="7" t="str">
-        <x:v>Not assessed</x:v>
+        <x:v>Resolve this line within the 8 October commercial review. Service and storage questions remain separate.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="42" customHeight="1">
@@ -6095,7 +6095,7 @@
         <x:v>Work state</x:v>
       </x:c>
       <x:c r="B127" s="7" t="str">
-        <x:v>Open — reconciliation outstanding</x:v>
+        <x:v>8 October 2026: commercial lead agrees £60 credit CN82. Finance controller verifies the resulting £180 net charge.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="60" customHeight="1">
@@ -6103,7 +6103,7 @@
         <x:v>Verification method</x:v>
       </x:c>
       <x:c r="B128" s="7" t="str">
-        <x:v>Check any agreed resolution against the reconciled activity and resulting invoice or credit record. Requirements and reviewer remain to be agreed.</x:v>
+        <x:v>Reconcile the 120 pallet-days to signed rate v2 and check £240 invoice less £60 credit CN82 equals £180.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="42" customHeight="1">
@@ -6111,7 +6111,7 @@
         <x:v>Verification owner</x:v>
       </x:c>
       <x:c r="B129" s="7" t="str">
-        <x:v>Not yet assigned</x:v>
+        <x:v>Finance controller</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="42" customHeight="1">
@@ -6119,7 +6119,7 @@
         <x:v>Verification date</x:v>
       </x:c>
       <x:c r="B130" s="7" t="str">
-        <x:v>Not yet agreed</x:v>
+        <x:v>8 October 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="42" customHeight="1">
@@ -6127,7 +6127,7 @@
         <x:v>Verification result</x:v>
       </x:c>
       <x:c r="B131" s="7" t="str">
-        <x:v>Pending — no entitlement or resolution conclusion</x:v>
+        <x:v>Verified: net £180 agrees with 120 pallet-days at £1.50. The billing correction is closed for this line.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="42" customHeight="1">
@@ -6135,7 +6135,7 @@
         <x:v>Decision / resources needed</x:v>
       </x:c>
       <x:c r="B132" s="7" t="str">
-        <x:v>Resolve any outstanding commercial interpretation and present it alongside the service and storage evidence.</x:v>
+        <x:v>Accept the verified credit for this line. Commercial lead checks contract timetable/options while the director awaits service and quality evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="42" customHeight="1">
@@ -6143,7 +6143,7 @@
         <x:v>Decision owner</x:v>
       </x:c>
       <x:c r="B133" s="7" t="str">
-        <x:v>Commercial/finance authority to be established; logistics director for renewal</x:v>
+        <x:v>Commercial lead for the credit; logistics director for the separate final renewal decision.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="30" customHeight="1">
@@ -6155,7 +6155,7 @@
         <x:v>Management note</x:v>
       </x:c>
       <x:c r="B135" s="7" t="str">
-        <x:v>The director's renewal decision remains open. A service finding does not settle storage acceptability, provider qualification or invoice entitlement.</x:v>
+        <x:v>As at 8 October, the director awaits the quality assessment due 9 October and service plan due 10 October. Commercial lead checks contract timetable/options. The verified £60 credit does not settle renewal or product acceptability.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="30" customHeight="1">
